--- a/backend/fms_core/tests/valid_templates/Container_creation_v4_2_0.xlsx
+++ b/backend/fms_core/tests/valid_templates/Container_creation_v4_2_0.xlsx
@@ -503,8 +503,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultColWidth="12.6171875" defaultRowHeight="14" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1001"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="14" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="22.33"/>
@@ -612,29 +612,29 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
       <c r="F12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -701,7 +701,7 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1390,16 +1390,20 @@
       <c r="F106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="11"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
@@ -4969,9 +4973,13 @@
       <c r="A1000" s="4"/>
       <c r="B1000" s="4"/>
     </row>
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="4"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A8:A107" type="list">
+    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A8:A108" type="list">
       <formula1>Index!$A$2:$A$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4992,7 +5000,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A1013"/>
-  <sheetFormatPr defaultColWidth="12.6171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="0" width="9.33"/>
